--- a/data/trans_bre/P62-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P62-Edad-trans_bre.xlsx
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,05</t>
+          <t>-0,24; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,97</t>
+          <t>-0,03; 5,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 5,54</t>
+          <t>-0,6; 5,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 1000,5</t>
+          <t>-34,15; 1103,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 1064,97</t>
+          <t>-22,72; 1132,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 3,56</t>
+          <t>-3,95; 3,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,71</t>
+          <t>-1,98; 6,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 2,58</t>
+          <t>-5,21; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 5,91</t>
+          <t>-16,08; 4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 225,37</t>
+          <t>-67,84; 280,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,82; 204,84</t>
+          <t>-27,35; 185,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 78,98</t>
+          <t>-63,58; 74,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,0; 182,54</t>
+          <t>-76,72; 111,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-44,36; -19,14</t>
+          <t>-45,69; -19,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,33; -3,08</t>
+          <t>-15,05; -3,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -0,04</t>
+          <t>-11,22; -0,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,84; -2,74</t>
+          <t>-26,69; -3,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,58; -74,63</t>
+          <t>-92,59; -75,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,53; -20,01</t>
+          <t>-66,31; -18,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 2,64</t>
+          <t>-62,5; 1,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,25; -15,13</t>
+          <t>-69,13; -16,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,52; -32,64</t>
+          <t>-56,96; -33,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,9; -9,9</t>
+          <t>-23,52; -9,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -9,95</t>
+          <t>-22,93; -9,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,84; -14,55</t>
+          <t>-33,23; -14,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-85,4; -69,98</t>
+          <t>-84,82; -69,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,38; -36,47</t>
+          <t>-66,58; -36,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,09; -40,28</t>
+          <t>-70,05; -40,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,33; -44,8</t>
+          <t>-69,9; -43,19</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-60,41; -46,34</t>
+          <t>-60,5; -46,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-46,76; -31,48</t>
+          <t>-47,39; -31,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,12; -26,9</t>
+          <t>-42,52; -26,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-39,97; -26,48</t>
+          <t>-40,12; -26,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,47; -62,12</t>
+          <t>-74,89; -62,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,35; -50,77</t>
+          <t>-68,0; -51,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,37; -44,41</t>
+          <t>-62,56; -44,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-57,75; -43,41</t>
+          <t>-58,11; -43,87</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,82; -41,07</t>
+          <t>-51,32; -41,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,06; -29,55</t>
+          <t>-40,55; -30,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,53; -30,26</t>
+          <t>-40,79; -29,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,68; 5,95</t>
+          <t>-27,74; 5,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-52,62; -41,9</t>
+          <t>-51,92; -41,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -29,75</t>
+          <t>-40,66; -30,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -30,75</t>
+          <t>-41,23; -30,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 7,42</t>
+          <t>-32,32; 6,1</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,89; -20,18</t>
+          <t>-30,21; -20,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,08; -18,21</t>
+          <t>-27,16; -18,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -20,1</t>
+          <t>-30,83; -20,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -8,09</t>
+          <t>-16,5; -8,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,95; -20,21</t>
+          <t>-30,26; -20,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,17; -18,32</t>
+          <t>-27,3; -18,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,29; -20,3</t>
+          <t>-30,87; -20,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -9,56</t>
+          <t>-18,4; -9,63</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -26,51</t>
+          <t>-32,83; -26,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -12,06</t>
+          <t>-18,03; -12,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,16; -13,08</t>
+          <t>-18,94; -13,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 7,24</t>
+          <t>-18,09; 4,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,44; -50,7</t>
+          <t>-58,31; -50,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,05; -28,52</t>
+          <t>-39,4; -28,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -29,07</t>
+          <t>-39,55; -29,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 13,63</t>
+          <t>-32,63; 8,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P62-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P62-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>275,39%</t>
+          <t>248,46%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,94</t>
+          <t>-0,59; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,29</t>
+          <t>-0,16; 4,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 5,24</t>
+          <t>-0,2; 5,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,55</t>
+          <t>-0,58; 4,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 1103,27</t>
+          <t>-31,36; 1156,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 1132,7</t>
+          <t>-26,73; 1061,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,7</t>
+          <t>-3,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,76%</t>
+          <t>-31,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,81</t>
+          <t>-3,97; 3,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,46</t>
+          <t>-2,11; 6,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,59</t>
+          <t>-5,51; 1,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 4,51</t>
+          <t>-13,16; 4,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 280,99</t>
+          <t>-72,52; 251,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 185,76</t>
+          <t>-30,52; 160,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 74,94</t>
+          <t>-67,56; 51,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,72; 111,2</t>
+          <t>-75,66; 118,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-13,55</t>
+          <t>-13,09</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-49,15%</t>
+          <t>-50,38%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-45,69; -19,18</t>
+          <t>-43,86; -19,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,05; -3,06</t>
+          <t>-15,3; -3,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,22; -0,06</t>
+          <t>-11,36; -0,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -3,41</t>
+          <t>-24,45; -2,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-92,59; -75,52</t>
+          <t>-92,15; -74,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,31; -18,37</t>
+          <t>-66,93; -21,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,5; 1,48</t>
+          <t>-61,95; -5,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-69,13; -16,61</t>
+          <t>-68,95; -12,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,14</t>
+          <t>-23,88</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-60,03%</t>
+          <t>-59,08%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,96; -33,56</t>
+          <t>-55,89; -32,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,52; -9,66</t>
+          <t>-24,25; -9,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,93; -9,79</t>
+          <t>-23,31; -10,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,23; -14,16</t>
+          <t>-33,16; -14,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-84,82; -69,7</t>
+          <t>-84,98; -69,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -36,31</t>
+          <t>-68,49; -36,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,05; -40,22</t>
+          <t>-69,44; -41,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,9; -43,19</t>
+          <t>-70,12; -44,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-33,44</t>
+          <t>-32,76</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-51,22%</t>
+          <t>-50,78%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-60,5; -46,64</t>
+          <t>-60,54; -46,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-47,39; -31,64</t>
+          <t>-46,69; -31,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,52; -26,88</t>
+          <t>-41,91; -26,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -26,74</t>
+          <t>-39,46; -25,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-74,89; -62,48</t>
+          <t>-75,06; -62,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-68,0; -51,22</t>
+          <t>-68,07; -51,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -44,71</t>
+          <t>-61,77; -44,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,11; -43,87</t>
+          <t>-57,2; -42,59</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,95</t>
+          <t>-25,72</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-14,01%</t>
+          <t>-30,09%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-51,32; -41,09</t>
+          <t>-51,58; -41,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,55; -30,06</t>
+          <t>-40,09; -29,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,79; -29,98</t>
+          <t>-40,35; -29,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 5,07</t>
+          <t>-30,6; -21,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -41,74</t>
+          <t>-52,25; -41,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-40,66; -30,2</t>
+          <t>-40,12; -29,9</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,23; -30,55</t>
+          <t>-41,15; -30,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 6,1</t>
+          <t>-35,07; -25,22</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-12,51</t>
+          <t>-12,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-14,23%</t>
+          <t>-14,04%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-30,21; -20,39</t>
+          <t>-30,55; -20,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-27,16; -18,21</t>
+          <t>-27,19; -18,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-30,83; -20,19</t>
+          <t>-29,72; -19,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -8,23</t>
+          <t>-16,54; -8,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-30,26; -20,52</t>
+          <t>-30,73; -20,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,3; -18,5</t>
+          <t>-27,3; -18,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,87; -20,38</t>
+          <t>-29,96; -20,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -9,63</t>
+          <t>-18,47; -9,62</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-10,84</t>
+          <t>-18,29</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-20,03%</t>
+          <t>-33,17%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -26,46</t>
+          <t>-32,87; -26,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,03; -12,27</t>
+          <t>-17,89; -11,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,94; -13,36</t>
+          <t>-19,13; -12,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-18,09; 4,22</t>
+          <t>-21,47; -14,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,31; -50,77</t>
+          <t>-58,51; -50,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,4; -28,52</t>
+          <t>-39,21; -27,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,55; -29,79</t>
+          <t>-39,94; -29,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,63; 8,05</t>
+          <t>-37,45; -28,23</t>
         </is>
       </c>
     </row>
